--- a/mosip_master/xlsx/applicant_valid_document.xlsx
+++ b/mosip_master/xlsx/applicant_valid_document.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\SLUDI Offline Training\sludi-mosip-data\mosip_master\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83A08466-CB86-42CF-9EEB-FCC9C62A920A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6460FB8B-DF96-416E-A35E-7D3596826832}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$52</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$50</definedName>
   </definedNames>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="60">
   <si>
     <t>lang_code</t>
   </si>
@@ -112,13 +112,109 @@
   </si>
   <si>
     <t>sin</t>
+  </si>
+  <si>
+    <t>017</t>
+  </si>
+  <si>
+    <t>018</t>
+  </si>
+  <si>
+    <t>019</t>
+  </si>
+  <si>
+    <t>020</t>
+  </si>
+  <si>
+    <t>021</t>
+  </si>
+  <si>
+    <t>022</t>
+  </si>
+  <si>
+    <t>023</t>
+  </si>
+  <si>
+    <t>024</t>
+  </si>
+  <si>
+    <t>025</t>
+  </si>
+  <si>
+    <t>026</t>
+  </si>
+  <si>
+    <t>027</t>
+  </si>
+  <si>
+    <t>028</t>
+  </si>
+  <si>
+    <t>029</t>
+  </si>
+  <si>
+    <t>030</t>
+  </si>
+  <si>
+    <t>031</t>
+  </si>
+  <si>
+    <t>032</t>
+  </si>
+  <si>
+    <t>033</t>
+  </si>
+  <si>
+    <t>034</t>
+  </si>
+  <si>
+    <t>035</t>
+  </si>
+  <si>
+    <t>036</t>
+  </si>
+  <si>
+    <t>037</t>
+  </si>
+  <si>
+    <t>038</t>
+  </si>
+  <si>
+    <t>039</t>
+  </si>
+  <si>
+    <t>040</t>
+  </si>
+  <si>
+    <t>041</t>
+  </si>
+  <si>
+    <t>042</t>
+  </si>
+  <si>
+    <t>043</t>
+  </si>
+  <si>
+    <t>044</t>
+  </si>
+  <si>
+    <t>045</t>
+  </si>
+  <si>
+    <t>046</t>
+  </si>
+  <si>
+    <t>047</t>
+  </si>
+  <si>
+    <t>048</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -130,6 +226,12 @@
       <b/>
       <sz val="11"/>
       <name val="Cambria"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <charset val="1"/>
     </font>
   </fonts>
@@ -491,7 +593,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E52"/>
+  <dimension ref="A1:E50"/>
   <sheetFormatPr defaultColWidth="8.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="8.44140625" style="1"/>
@@ -809,7 +911,7 @@
         <v>27</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C19" t="s">
         <v>7</v>
@@ -826,7 +928,7 @@
         <v>27</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="C20" t="s">
         <v>7</v>
@@ -843,7 +945,7 @@
         <v>27</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="C21" t="s">
         <v>7</v>
@@ -860,7 +962,7 @@
         <v>27</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="C22" t="s">
         <v>7</v>
@@ -877,7 +979,7 @@
         <v>27</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="C23" t="s">
         <v>7</v>
@@ -894,7 +996,7 @@
         <v>27</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="C24" t="s">
         <v>7</v>
@@ -911,7 +1013,7 @@
         <v>27</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C25" t="s">
         <v>7</v>
@@ -928,7 +1030,7 @@
         <v>27</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="C26" t="s">
         <v>7</v>
@@ -945,7 +1047,7 @@
         <v>27</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C27" t="s">
         <v>7</v>
@@ -962,7 +1064,7 @@
         <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="C28" t="s">
         <v>7</v>
@@ -979,7 +1081,7 @@
         <v>27</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="C29" t="s">
         <v>7</v>
@@ -996,7 +1098,7 @@
         <v>27</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="C30" t="s">
         <v>7</v>
@@ -1013,7 +1115,7 @@
         <v>27</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="C31" t="s">
         <v>7</v>
@@ -1030,7 +1132,7 @@
         <v>27</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="C32" t="s">
         <v>7</v>
@@ -1047,7 +1149,7 @@
         <v>27</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="C33" t="s">
         <v>7</v>
@@ -1064,7 +1166,7 @@
         <v>27</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="C34" t="s">
         <v>7</v>
@@ -1078,10 +1180,10 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="C35" t="s">
         <v>7</v>
@@ -1098,7 +1200,7 @@
         <v>24</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="C36" t="s">
         <v>7</v>
@@ -1115,7 +1217,7 @@
         <v>24</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>6</v>
+        <v>46</v>
       </c>
       <c r="C37" t="s">
         <v>7</v>
@@ -1132,7 +1234,7 @@
         <v>24</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>9</v>
+        <v>47</v>
       </c>
       <c r="C38" t="s">
         <v>7</v>
@@ -1149,7 +1251,7 @@
         <v>24</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="C39" t="s">
         <v>7</v>
@@ -1166,7 +1268,7 @@
         <v>24</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>11</v>
+        <v>49</v>
       </c>
       <c r="C40" t="s">
         <v>7</v>
@@ -1183,7 +1285,7 @@
         <v>24</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="C41" t="s">
         <v>7</v>
@@ -1200,7 +1302,7 @@
         <v>24</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>13</v>
+        <v>51</v>
       </c>
       <c r="C42" t="s">
         <v>7</v>
@@ -1217,7 +1319,7 @@
         <v>24</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>14</v>
+        <v>52</v>
       </c>
       <c r="C43" t="s">
         <v>7</v>
@@ -1234,7 +1336,7 @@
         <v>24</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>15</v>
+        <v>53</v>
       </c>
       <c r="C44" t="s">
         <v>7</v>
@@ -1251,7 +1353,7 @@
         <v>24</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>16</v>
+        <v>54</v>
       </c>
       <c r="C45" t="s">
         <v>7</v>
@@ -1268,7 +1370,7 @@
         <v>24</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>17</v>
+        <v>55</v>
       </c>
       <c r="C46" t="s">
         <v>7</v>
@@ -1285,7 +1387,7 @@
         <v>24</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>18</v>
+        <v>56</v>
       </c>
       <c r="C47" t="s">
         <v>7</v>
@@ -1302,7 +1404,7 @@
         <v>24</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>19</v>
+        <v>57</v>
       </c>
       <c r="C48" t="s">
         <v>7</v>
@@ -1319,7 +1421,7 @@
         <v>24</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>20</v>
+        <v>58</v>
       </c>
       <c r="C49" t="s">
         <v>7</v>
@@ -1336,7 +1438,7 @@
         <v>24</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>21</v>
+        <v>59</v>
       </c>
       <c r="C50" t="s">
         <v>7</v>
@@ -1348,42 +1450,9 @@
         <v>8</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A51" t="s">
-        <v>24</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C51" t="s">
-        <v>7</v>
-      </c>
-      <c r="D51" t="s">
-        <v>26</v>
-      </c>
-      <c r="E51" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A52" t="s">
-        <v>24</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C52" t="s">
-        <v>7</v>
-      </c>
-      <c r="D52" t="s">
-        <v>26</v>
-      </c>
-      <c r="E52" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:E52" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:E50" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555496" footer="0.51180555555555496"/>
   <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
